--- a/10_ToMONGOLICA/04_Admixture/01_FullAdmixture/04_STR_Stats.xlsx
+++ b/10_ToMONGOLICA/04_Admixture/01_FullAdmixture/04_STR_Stats.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmohn\Desktop\10_Analysis\02_STRUCTURE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmohn\Documents\GitHub\QMacGs\10_ToMONGOLICA\04_Admixture\01_FullAdmixture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0D4276-F41B-4E4D-844E-AB38A19152C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC95938-EFBF-4FCF-AA00-E6444FE6C2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2511" yWindow="1929" windowWidth="14375" windowHeight="8065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -479,37 +479,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -521,7 +491,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -532,11 +502,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -660,6 +630,8 @@
         <c:axId val="497410352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="20"/>
+          <c:min val="4"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -677,6 +649,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>K</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -739,6 +766,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>CV</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> error</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
